--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487974_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487974_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.243</v>
+        <v>12.3483</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4537</v>
+        <v>8.8009</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7893</v>
+        <v>3.5474</v>
       </c>
       <c r="G2" t="n">
         <v>9.398</v>
@@ -610,13 +610,13 @@
         <v>1.784</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5606</v>
+        <v>2.6659</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.121</v>
+        <v>1.2262</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6816</v>
+        <v>1.4397</v>
       </c>
       <c r="V2" t="n">
         <v>1.4737</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.2204</v>
+        <v>7.9877</v>
       </c>
       <c r="E3" t="n">
-        <v>4.6741</v>
+        <v>4.6568</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5462</v>
+        <v>3.331</v>
       </c>
       <c r="G3" t="n">
-        <v>4.683</v>
+        <v>4.4059</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9139</v>
+        <v>0.6427</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7691</v>
+        <v>3.7632</v>
       </c>
       <c r="J3" t="n">
-        <v>4.103</v>
+        <v>4.0316</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2152</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8878</v>
+        <v>3.3386</v>
       </c>
       <c r="M3" t="n">
-        <v>0.58</v>
+        <v>0.3743</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6988</v>
+        <v>-0.0503</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1187</v>
+        <v>0.4246</v>
       </c>
       <c r="P3" t="n">
-        <v>-5.7485</v>
+        <v>0.3964</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7.136</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
         <v>1.3876</v>
       </c>
       <c r="S3" t="n">
-        <v>6.9421</v>
+        <v>3.1854</v>
       </c>
       <c r="T3" t="n">
-        <v>5.3634</v>
+        <v>1.6163</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5787</v>
+        <v>1.5691</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3438</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3438</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>7.41</v>
+        <v>5.1529</v>
       </c>
       <c r="E4" t="n">
-        <v>3.349</v>
+        <v>1.5786</v>
       </c>
       <c r="F4" t="n">
-        <v>4.061</v>
+        <v>3.5743</v>
       </c>
       <c r="G4" t="n">
-        <v>4.4059</v>
+        <v>4.683</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6427</v>
+        <v>3.9139</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7632</v>
+        <v>0.7691</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0316</v>
+        <v>4.103</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6929999999999999</v>
+        <v>3.2152</v>
       </c>
       <c r="L4" t="n">
-        <v>3.3386</v>
+        <v>0.8878</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3743</v>
+        <v>0.58</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0503</v>
+        <v>0.6988</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4246</v>
+        <v>-0.1187</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3964</v>
+        <v>-5.7485</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>-7.136</v>
       </c>
       <c r="R4" t="n">
         <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6077</v>
+        <v>3.8746</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3085</v>
+        <v>2.2678</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2991</v>
+        <v>1.6067</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.3438</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.3438</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. BELEMENE DZABATOU</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.8423</v>
+        <v>3.5311</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1925</v>
+        <v>0.6978</v>
       </c>
       <c r="F5" t="n">
-        <v>3.6499</v>
+        <v>2.8333</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2245</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.1914</v>
+        <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9669</v>
+        <v>-1.2299</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4107</v>
+        <v>-0.4541</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.3547</v>
+        <v>0.9287</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9441</v>
+        <v>-1.3829</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1861</v>
+        <v>0.4442</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1633</v>
+        <v>0.2913</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0228</v>
+        <v>0.1529</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1716</v>
+        <v>-1.1893</v>
       </c>
       <c r="R5" t="n">
         <v>1.3876</v>
       </c>
       <c r="S5" t="n">
-        <v>6.8509</v>
+        <v>3.6094</v>
       </c>
       <c r="T5" t="n">
-        <v>4.5081</v>
+        <v>2.3413</v>
       </c>
       <c r="U5" t="n">
-        <v>2.3428</v>
+        <v>1.2681</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2666</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6058</v>
+        <v>2.2565</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9339</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6648</v>
+        <v>1.3226</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.3562</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22</v>
+        <v>0.8219</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2299</v>
+        <v>-1.1781</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4541</v>
+        <v>-0.0611</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9287</v>
+        <v>0.8682</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3829</v>
+        <v>-0.9293</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4442</v>
+        <v>-0.2952</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2913</v>
+        <v>-0.0463</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1529</v>
+        <v>-0.2488</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>3.6841</v>
+        <v>2.476</v>
       </c>
       <c r="T6" t="n">
-        <v>2.5845</v>
+        <v>1.4529</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0996</v>
+        <v>1.0231</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MARTOS BONACHELA</t>
+          <t>C. BELEMENE DZABATOU</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5145</v>
+        <v>1.4524</v>
       </c>
       <c r="E7" t="n">
-        <v>0.518</v>
+        <v>-1.7201</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0036</v>
+        <v>3.1725</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4411</v>
+        <v>-1.2245</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2018</v>
+        <v>-3.1914</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6428</v>
+        <v>1.9669</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6428</v>
+        <v>-1.4107</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-3.3547</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6428</v>
+        <v>1.9441</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2018</v>
+        <v>0.1861</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2018</v>
+        <v>0.1633</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.0228</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1982</v>
+        <v>-1.784</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.1716</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1248</v>
+        <v>4.461</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1248</v>
+        <v>2.5955</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8655</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS  LAJARA</t>
+          <t>A. MARTOS BONACHELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,55 +1033,55 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3027</v>
+        <v>0.6788</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3027</v>
+        <v>0.6823</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.0036</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3027</v>
+        <v>0.4411</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3027</v>
+        <v>-0.2018</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.6428</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3027</v>
+        <v>0.6428</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3027</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6428</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-0.2018</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.2018</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.0395</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.0395</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>S. TORRECILLAS  LAJARA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2603</v>
+        <v>0.3027</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3302</v>
+        <v>0.3027</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0699</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3562</v>
+        <v>0.3027</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8219</v>
+        <v>0.3027</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1781</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0611</v>
+        <v>0.3027</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8682</v>
+        <v>0.3027</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9293</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2952</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0463</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2488</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3964</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5947</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0408</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8112</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7704</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. REQUENA ESCABIAS</t>
+          <t>S. TORRECILLAS LAJARA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7865</v>
+        <v>-0.4617</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1268</v>
+        <v>-1.1815</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6597</v>
+        <v>0.7198</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0056</v>
+        <v>-1.1637</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0458</v>
+        <v>-0.2933</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0402</v>
+        <v>-0.8704</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0604</v>
+        <v>-1.2375</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0202</v>
+        <v>0.0404</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0402</v>
+        <v>-1.2779</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.066</v>
+        <v>0.0738</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.066</v>
+        <v>-0.3337</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.4075</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1685</v>
+        <v>0.3056</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1872</v>
+        <v>0.056</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0187</v>
+        <v>0.2496</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>R. REQUENA ESCABIAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-0.5942</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2387</v>
+        <v>0.0374</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6116</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5337</v>
+        <v>-0.0056</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4788</v>
+        <v>-0.0458</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.0125</v>
+        <v>0.0402</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.9568</v>
+        <v>0.0604</v>
       </c>
       <c r="K11" t="n">
-        <v>0.599</v>
+        <v>0.0202</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5558</v>
+        <v>0.0402</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4232</v>
+        <v>-0.066</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1201</v>
+        <v>-0.066</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5433</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9911</v>
+        <v>0.5947</v>
       </c>
       <c r="S11" t="n">
-        <v>2.3047</v>
+        <v>0.0239</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9164</v>
+        <v>-0.0229</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3883</v>
+        <v>0.0468</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4142</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. TORRECILLAS LAJARA</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-0.8459</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.5495</v>
+        <v>-0.459</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6075</v>
+        <v>-0.387</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.1637</v>
+        <v>-1.5337</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2933</v>
+        <v>0.4788</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8704</v>
+        <v>-2.0125</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.2375</v>
+        <v>-1.9568</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0404</v>
+        <v>0.599</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2779</v>
+        <v>-2.5558</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0738</v>
+        <v>0.4232</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3337</v>
+        <v>-0.1201</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4075</v>
+        <v>0.5433</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3964</v>
+        <v>0.9911</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1747</v>
+        <v>2.309</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.312</v>
+        <v>1.6961</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1373</v>
+        <v>0.6129</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7222</v>
+        <v>-2.9832</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.3441</v>
+        <v>-3.2401</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6219</v>
+        <v>0.2569</v>
       </c>
       <c r="G13" t="n">
         <v>-4.6857</v>
@@ -1468,13 +1468,13 @@
         <v>0.7929</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3005</v>
+        <v>3.0395</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4957</v>
+        <v>1.5997</v>
       </c>
       <c r="U13" t="n">
-        <v>1.8047</v>
+        <v>1.4397</v>
       </c>
       <c r="V13" t="n">
         <v>-0.9405</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>27.5774</v>
+        <v>28.82539999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>9.841699999999999</v>
+        <v>11.0897</v>
       </c>
       <c r="F14" t="n">
-        <v>17.7356</v>
+        <v>17.73560000000001</v>
       </c>
       <c r="G14" t="n">
         <v>10.2514</v>
@@ -1516,22 +1516,22 @@
         <v>3.065900000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>7.185400000000001</v>
+        <v>7.185399999999998</v>
       </c>
       <c r="J14" t="n">
-        <v>8.573999999999998</v>
+        <v>8.574</v>
       </c>
       <c r="K14" t="n">
-        <v>2.889600000000002</v>
+        <v>2.8896</v>
       </c>
       <c r="L14" t="n">
-        <v>5.684500000000002</v>
+        <v>5.6845</v>
       </c>
       <c r="M14" t="n">
         <v>1.6773</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1765999999999996</v>
+        <v>0.1766000000000001</v>
       </c>
       <c r="O14" t="n">
         <v>1.5009</v>
@@ -1546,10 +1546,10 @@
         <v>10.9024</v>
       </c>
       <c r="S14" t="n">
-        <v>24.7418</v>
+        <v>25.9898</v>
       </c>
       <c r="T14" t="n">
-        <v>13.6204</v>
+        <v>14.8684</v>
       </c>
       <c r="U14" t="n">
         <v>11.1212</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.791</v>
+        <v>1.7022</v>
       </c>
       <c r="E15" t="n">
         <v>0.0709</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7201</v>
+        <v>1.6313</v>
       </c>
       <c r="G15" t="n">
         <v>2.179</v>
@@ -1624,13 +1624,13 @@
         <v>1.784</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.0513</v>
+        <v>-2.1401</v>
       </c>
       <c r="T15" t="n">
         <v>-0.9984</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.053</v>
+        <v>-1.1418</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1207</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.208</v>
+        <v>-1.1238</v>
       </c>
       <c r="E18" t="n">
         <v>-1.2627</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0548</v>
+        <v>0.139</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0858</v>
@@ -1858,13 +1858,13 @@
         <v>0.3964</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5275</v>
+        <v>-0.4432</v>
       </c>
       <c r="T18" t="n">
         <v>-0.312</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2155</v>
+        <v>-0.1313</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.65</v>
+        <v>-2.697</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.9445</v>
+        <v>-3.352</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2945</v>
+        <v>0.655</v>
       </c>
       <c r="G19" t="n">
         <v>-0.4935</v>
@@ -1936,13 +1936,13 @@
         <v>2.7751</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.0952</v>
+        <v>-3.1423</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.068</v>
+        <v>-1.4755</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.0273</v>
+        <v>-1.6668</v>
       </c>
       <c r="V19" t="n">
         <v>0.1459</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. GEA BECERRA</t>
+          <t>J. MARTIN GONZALEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.841</v>
+        <v>-3.0247</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1737</v>
+        <v>-2.8812</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.6674</v>
+        <v>-0.1436</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.4331</v>
+        <v>-1.6787</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2279</v>
+        <v>-0.6836</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.661</v>
+        <v>-0.9951</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5137</v>
+        <v>-1.4121</v>
       </c>
       <c r="K20" t="n">
-        <v>1.353</v>
+        <v>-0.094</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1607</v>
+        <v>-1.3181</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.9468</v>
+        <v>-0.2667</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1251</v>
+        <v>-0.5896</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8217</v>
+        <v>0.323</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1805</v>
+        <v>-0.1982</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3787</v>
+        <v>1.784</v>
       </c>
       <c r="S20" t="n">
-        <v>-3.4168</v>
+        <v>-3.2185</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3176</v>
+        <v>-1.2709</v>
       </c>
       <c r="U20" t="n">
-        <v>-2.0992</v>
+        <v>-1.9476</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8107</v>
+        <v>0.2867</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.2867</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MARTIN GONZALEZ</t>
+          <t>E. GEA BECERRA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6555</v>
+        <v>-3.0905</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.983</v>
+        <v>-0.4793</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6725</v>
+        <v>-2.6112</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.6787</v>
+        <v>-1.4331</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6836</v>
+        <v>0.2279</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9951</v>
+        <v>-1.661</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4121</v>
+        <v>1.5137</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.094</v>
+        <v>1.353</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3181</v>
+        <v>0.1607</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2667</v>
+        <v>-2.9468</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5896</v>
+        <v>-1.1251</v>
       </c>
       <c r="O21" t="n">
-        <v>0.323</v>
+        <v>-1.8217</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1982</v>
+        <v>-2.1805</v>
       </c>
       <c r="R21" t="n">
-        <v>1.784</v>
+        <v>2.3787</v>
       </c>
       <c r="S21" t="n">
-        <v>-3.8493</v>
+        <v>-3.6663</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3727</v>
+        <v>-1.6232</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.4765</v>
+        <v>-2.0431</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2867</v>
+        <v>1.8107</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X21" t="n">
-        <v>0.2867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7729</v>
+        <v>-3.321</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9561</v>
+        <v>-1.7523</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8169</v>
+        <v>-1.5687</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7392</v>
@@ -2170,13 +2170,13 @@
         <v>3.1716</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.0607</v>
+        <v>-4.6088</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.1839</v>
+        <v>-1.9802</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8768</v>
+        <v>-2.6286</v>
       </c>
       <c r="V22" t="n">
         <v>2.0269</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2149</v>
+        <v>-6.6335</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.682</v>
+        <v>-4.4782</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.533</v>
+        <v>-2.1553</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1083</v>
@@ -2248,13 +2248,13 @@
         <v>3.3698</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.435</v>
+        <v>-3.8535</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.1215</v>
+        <v>-1.9178</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.3135</v>
+        <v>-1.9358</v>
       </c>
       <c r="V23" t="n">
         <v>-1.861</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.7348</v>
+        <v>-10.4188</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3153</v>
+        <v>-5.1116</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.4195</v>
+        <v>-5.3072</v>
       </c>
       <c r="G24" t="n">
         <v>-7.5381</v>
@@ -2326,13 +2326,13 @@
         <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>-3.3683</v>
+        <v>-3.0523</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.7471</v>
+        <v>-1.5434</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.6212</v>
+        <v>-1.5089</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8107</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-27.5772</v>
+        <v>-26.8982</v>
       </c>
       <c r="E25" t="n">
         <v>-17.7357</v>
       </c>
       <c r="F25" t="n">
-        <v>-9.841699999999999</v>
+        <v>-9.1625</v>
       </c>
       <c r="G25" t="n">
         <v>-10.2512</v>
@@ -2404,13 +2404,13 @@
         <v>17.8401</v>
       </c>
       <c r="S25" t="n">
-        <v>-24.7417</v>
+        <v>-24.0626</v>
       </c>
       <c r="T25" t="n">
-        <v>-11.1212</v>
+        <v>-11.1214</v>
       </c>
       <c r="U25" t="n">
-        <v>-13.6206</v>
+        <v>-12.9415</v>
       </c>
       <c r="V25" t="n">
         <v>0.4778</v>
